--- a/CastleHero_Table/Character_Upgrade_Table.xlsx
+++ b/CastleHero_Table/Character_Upgrade_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\CH_Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDA5064-E4B8-4916-98D5-053796D81972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{181D1AC4-6DD4-4A9A-832D-F5E843E39EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="2590" windowWidth="30670" windowHeight="19010" xr2:uid="{9D156A71-7D71-4207-9C5E-77EBF3C29C25}"/>
+    <workbookView xWindow="7050" yWindow="1280" windowWidth="30700" windowHeight="19010" xr2:uid="{9D156A71-7D71-4207-9C5E-77EBF3C29C25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Character_ID</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -134,67 +134,6 @@
   </si>
   <si>
     <t>Rate_5_option_Value_2</t>
-  </si>
-  <si>
-    <t>캐릭터 ID</t>
-  </si>
-  <si>
-    <t>1레벨 당 체력 증가량</t>
-  </si>
-  <si>
-    <t>1레벨 당 공격력 증가량</t>
-  </si>
-  <si>
-    <t>1레벨 당 치명타 확률 증가량</t>
-  </si>
-  <si>
-    <t>1레벨 당 치명타 피해 증가량</t>
-  </si>
-  <si>
-    <t>1레벨 당 공격속도 증가량</t>
-  </si>
-  <si>
-    <t>1레벨 당 이동속도 증가량</t>
-  </si>
-  <si>
-    <t>1레벨 당 공격범위 증가량</t>
-  </si>
-  <si>
-    <t>1레벨 당 이동범위 증가량</t>
-  </si>
-  <si>
-    <t>★등급 일때 추가 옵션</t>
-  </si>
-  <si>
-    <t>_1 옵션의 값</t>
-  </si>
-  <si>
-    <t>★등급 추가 옵션</t>
-  </si>
-  <si>
-    <t>_2 옵션의 값</t>
-  </si>
-  <si>
-    <t>★★등급 추가 옵션</t>
-  </si>
-  <si>
-    <t>★★★등급 추가 옵션</t>
-  </si>
-  <si>
-    <t>★★★★등급 추가 옵션</t>
-  </si>
-  <si>
-    <t>★★★★★등급 추가 옵션</t>
-  </si>
-  <si>
-    <t>0 스킬
-1 공격력 증가
-2 체력 증가
-3 공격속도
-4 이동속도
-5 치명타율
-6 치명타 피해</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -285,7 +224,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -294,9 +233,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -635,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F499027E-1266-4967-BB3D-A677F344DFAC}">
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -669,201 +605,207 @@
     <col min="30" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="107.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="J1" s="3" t="s">
-        <v>46</v>
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2">
+        <v>10021</v>
+      </c>
+      <c r="B2" s="1">
         <v>30</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>41</v>
+      <c r="C2" s="1">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1">
+        <v>10</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1</v>
+      </c>
+      <c r="O2" s="1">
+        <v>100</v>
+      </c>
+      <c r="P2" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>10</v>
+      </c>
+      <c r="R2" s="1">
+        <v>0</v>
+      </c>
+      <c r="S2" s="1">
+        <v>10</v>
+      </c>
+      <c r="V2" s="1">
+        <v>1</v>
+      </c>
+      <c r="W2" s="1">
+        <v>100</v>
+      </c>
+      <c r="X2" s="1">
+        <v>3</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC3" s="4" t="s">
-        <v>28</v>
+      <c r="A3" s="2">
+        <v>20001</v>
+      </c>
+      <c r="B3" s="1">
+        <v>50</v>
+      </c>
+      <c r="C3" s="1">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
-        <v>10021</v>
+        <v>20002</v>
       </c>
       <c r="B4" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C4" s="1">
         <v>10</v>
       </c>
       <c r="D4" s="1">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E4" s="1">
         <v>0.05</v>
@@ -879,53 +821,11 @@
       </c>
       <c r="I4" s="1">
         <v>0</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>10</v>
-      </c>
-      <c r="N4" s="1">
-        <v>1</v>
-      </c>
-      <c r="O4" s="1">
-        <v>100</v>
-      </c>
-      <c r="P4" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>10</v>
-      </c>
-      <c r="R4" s="1">
-        <v>0</v>
-      </c>
-      <c r="S4" s="1">
-        <v>10</v>
-      </c>
-      <c r="V4" s="1">
-        <v>1</v>
-      </c>
-      <c r="W4" s="1">
-        <v>100</v>
-      </c>
-      <c r="X4" s="1">
-        <v>3</v>
-      </c>
-      <c r="Y4" s="1">
-        <v>10</v>
-      </c>
-      <c r="Z4" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="1">
-        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
-        <v>20001</v>
+        <v>20003</v>
       </c>
       <c r="B5" s="1">
         <v>50</v>
@@ -954,16 +854,16 @@
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
-        <v>20002</v>
+        <v>30003</v>
       </c>
       <c r="B6" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C6" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E6" s="1">
         <v>0.05</v>
@@ -980,103 +880,45 @@
       <c r="I6" s="1">
         <v>0</v>
       </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>10</v>
+      </c>
+      <c r="N6" s="1">
+        <v>2</v>
+      </c>
+      <c r="O6" s="1">
+        <v>300</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1">
+        <v>10</v>
+      </c>
+      <c r="V6" s="1">
+        <v>2</v>
+      </c>
+      <c r="W6" s="1">
+        <v>300</v>
+      </c>
+      <c r="X6" s="1">
+        <v>3</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A7" s="2">
-        <v>20003</v>
-      </c>
-      <c r="B7" s="1">
-        <v>50</v>
-      </c>
-      <c r="C7" s="1">
-        <v>10</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A8" s="2">
-        <v>30003</v>
-      </c>
-      <c r="B8" s="1">
-        <v>100</v>
-      </c>
-      <c r="C8" s="1">
-        <v>20</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-      <c r="J8" s="1">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>10</v>
-      </c>
-      <c r="N8" s="1">
-        <v>2</v>
-      </c>
-      <c r="O8" s="1">
-        <v>300</v>
-      </c>
-      <c r="R8" s="1">
-        <v>0</v>
-      </c>
-      <c r="S8" s="1">
-        <v>10</v>
-      </c>
-      <c r="V8" s="1">
-        <v>2</v>
-      </c>
-      <c r="W8" s="1">
-        <v>300</v>
-      </c>
-      <c r="X8" s="1">
-        <v>3</v>
-      </c>
-      <c r="Y8" s="1">
-        <v>10</v>
-      </c>
-      <c r="Z8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.45">
-      <c r="A9" s="2"/>
+      <c r="A7" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
